--- a/extracted/reports/tramos_filtrado_estricto/tramo_122+750_123+100.xlsx
+++ b/extracted/reports/tramos_filtrado_estricto/tramo_122+750_123+100.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -485,14 +485,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Filtro estricto: INICIO (KM) y FIN (KM) contenidos en el tramo | Total registros: 47</t>
+          <t>Filtro: FIN completo contenido en tramo; FIN en blanco si INICIO cae en tramo | Total registros: 83</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Año 2018 (1 registros)</t>
+          <t>Año 2018 (7 registros)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -564,47 +564,55 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Año 2019 (9 registros)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>2018-03-24</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>123+050</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2018-04-25</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>122+945</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -620,27 +628,23 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2018-12-29</t>
+          <t>2018-08-02</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>123+000</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>123+100</t>
-        </is>
-      </c>
+          <t>122+800</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Reparación de Bache Superficial T2</t>
+          <t>Repintado de Postes de (hitos) kilométricos T2</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -650,27 +654,23 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>122+799</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>122+799</t>
-        </is>
-      </c>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Reparación de Bache Superficial T2</t>
+          <t>Repintado de Parapetos Muros T2</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -680,27 +680,23 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>122+837</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>122+837</t>
-        </is>
-      </c>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Reparación de Bache Superficial T2</t>
+          <t>Repintado de Parapetos Muros T2</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -710,107 +706,87 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>122+857</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>122+857</t>
-        </is>
-      </c>
+          <t>123+040</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Reparación de Bache Superficial T2</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>122+920</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>122+920</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.04000000000000001</v>
-      </c>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Año 2019 (20 registros)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Reparación de Bache Superficial T2</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>122+924</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>122+924</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.04000000000000001</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2018-12-29</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>122+800</t>
+          <t>123+000</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>122+900</t>
+          <t>123+100</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
@@ -820,17 +796,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2019-03-06</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -838,19 +814,15 @@
           <t>122+900</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>123+000</t>
-        </is>
-      </c>
+      <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -860,141 +832,149 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2019-12-25</t>
+          <t>2019-05-28</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>122+800</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>122+806</t>
-        </is>
-      </c>
+          <t>123+045</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Año 2021 (7 registros)</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Reparación de Cuneta Urbana tipo 1 T2</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>2019-05-28</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>123+053</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Reparación de Bache Superficial T2</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>2019-06-25</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>122+799</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>122+799</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.04000000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Reparación de Bache Superficial T2</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>122+890</t>
+          <t>122+837</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>122+900</t>
+          <t>122+837</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>10</v>
+        <v>0.04000000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Reparación de Bache Superficial T2</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>122+800</t>
+          <t>122+857</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>122+920</t>
+          <t>122+857</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>120</v>
+        <v>0.04000000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Reparación de Bache Superficial T2</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1004,17 +984,17 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>123+050</t>
+          <t>122+920</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>130</v>
+        <v>0.04000000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Residuos Sólidos / Basuras</t>
+          <t>Reparación de Bache Superficial T2</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1024,215 +1004,211 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>122+885</t>
+          <t>122+924</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>122+915</t>
+          <t>122+924</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>30</v>
+        <v>0.04000000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Reposición de Señalización Vertical T2</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2019-07-04</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>122+952</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>122+995</t>
-        </is>
-      </c>
+          <t>122+906</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n">
-        <v>43</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2019-07-10</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>123+025</t>
+          <t>122+800</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>123+100</t>
+          <t>122+900</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2019-07-10</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>122+880</t>
+          <t>122+900</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>122+881</t>
+          <t>123+000</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Año 2022 (7 registros)</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Reposición de cunetas T2</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>2019-07-12</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>122+915</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Reposición de cunetas T2</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>2019-07-22</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>122+915</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2019-09-30</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>122+780</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>122+803</t>
-        </is>
-      </c>
+          <t>122+752</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Desbroce Manual T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2019-09-30</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>122+860</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>122+880</t>
-        </is>
-      </c>
+          <t>122+875</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -1248,51 +1224,43 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2022-02-21</t>
+          <t>2019-09-30</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>123+000</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>123+100</t>
-        </is>
-      </c>
+          <t>122+945</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2019-09-30</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>122+786</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>122+800</t>
-        </is>
-      </c>
+          <t>122+947</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -1308,131 +1276,123 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2019-09-30</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>122+951</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>122+985</t>
-        </is>
-      </c>
+          <t>122+950</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Pintura Chevron Guarda Vías T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2019-12-25</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>122+962</t>
+          <t>122+800</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>122+985</t>
+          <t>122+806</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza Residuos Sólidos / Basuras</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>122+780</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>122+980</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>200</v>
-      </c>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Año 2020 (2 registros)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Año 2023 (9 registros)</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>2020-01-18</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>122+960</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -1442,237 +1402,201 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>2023-02-15</t>
+          <t>2020-01-18</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>122+816</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>122+830</t>
-        </is>
-      </c>
+          <t>123+042</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
       <c r="F38" s="5" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>2023-02-15</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>122+913</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>123+000</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>87</v>
-      </c>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Año 2021 (15 registros)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza Residuos Sólidos / Basuras</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>122+930</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>122+930</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>80</v>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Repintado de Postes de (hitos) kilométricos T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>123+000</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>123+000</t>
-        </is>
-      </c>
+          <t>122+800</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
       <c r="F41" s="5" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Repintado de Parapetos Muros T2</t>
+          <t>Limpieza de Juntas en Cunetas y Bermas</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>123+044</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>123+046</t>
-        </is>
-      </c>
+          <t>122+800</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n"/>
       <c r="F42" s="5" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>122+766</t>
+          <t>122+890</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>122+800</t>
+          <t>122+900</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Delineador T2</t>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>122+790</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>122+792</t>
-        </is>
-      </c>
+          <t>123+040</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
       <c r="F44" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Delineador T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>122+875</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>122+876</t>
-        </is>
-      </c>
+          <t>123+050</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n"/>
       <c r="F45" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Guardavías T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -1682,101 +1606,113 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>122+900</t>
+          <t>122+800</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>123+000</t>
+          <t>122+920</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Año 2024 (2 registros)</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>2021-06-14</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>122+920</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>123+050</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Cajas de Inspección Subdren T2</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>2021-06-14</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>122+920</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Limpieza Residuos Sólidos / Basuras</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>123+030</t>
+          <t>122+885</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>123+100</t>
+          <t>122+915</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1786,65 +1722,77 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>123+044</t>
+          <t>122+952</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>123+046</t>
+          <t>122+995</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Año 2025 (7 registros)</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>2021-10-11</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>123+025</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>123+100</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>122+756</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -1860,51 +1808,43 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>122+750</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>122+800</t>
-        </is>
-      </c>
+          <t>122+915</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n"/>
       <c r="F53" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>122+900</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>123+000</t>
-        </is>
-      </c>
+          <t>122+943</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n"/>
       <c r="F54" s="5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
@@ -1920,251 +1860,239 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>122+870</t>
+          <t>122+880</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>123+020</t>
+          <t>122+881</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Reparación de Bache Superficial T2</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>122+900</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>122+935</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>4</v>
-      </c>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Año 2022 (14 registros)</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>123+060</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>123+060</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>14</v>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Reposición de Delineador T2</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>und</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>122+900</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>123+000</t>
-        </is>
-      </c>
+          <t>122+779</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n"/>
       <c r="F58" s="5" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Residuos Sólidos / Basuras</t>
+          <t>Limpieza mecanizada de cabezal de alcantarilla T2</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>2022-01-07</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>122+780</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>122+803</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Desbroce Manual T2</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
           <t>m2</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>123+060</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>123+085</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Año 2026 (5 registros)</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>2022-01-07</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>122+860</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>122+880</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>2022-02-21</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>123+100</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Repintado de Postes de (hitos) kilométricos T2</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>122+960</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
           <t>123+000</t>
         </is>
       </c>
+      <c r="E62" s="5" t="n"/>
       <c r="F62" s="5" t="n">
-        <v>40</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>122+980</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>123+000</t>
-        </is>
-      </c>
+          <t>123+038</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n"/>
       <c r="F63" s="5" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Reparación de Bache Superficial T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -2174,95 +2102,1148 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>122+790</t>
+          <t>122+786</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>122+790</t>
+          <t>122+800</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Pintura Chevron Guarda Vías T2</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>122+800</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>122+999</t>
-        </is>
-      </c>
+          <t>122+796</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n"/>
       <c r="F65" s="5" t="n">
-        <v>100</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Repintado de Parapetos Muros T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>122+945</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>122+940</t>
-        </is>
-      </c>
+          <t>122+895</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n"/>
       <c r="F66" s="5" t="n">
         <v>12</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>122+951</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>122+985</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Pintura Chevron Guarda Vías T2</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>122+962</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>122+985</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Pintura Chevron Guarda Vías T2</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>122+812</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>122+942</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Residuos Sólidos / Basuras</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>122+780</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>122+980</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Año 2023 (9 registros)</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>2023-02-15</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>122+816</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>122+830</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>2023-02-15</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>122+913</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Residuos Sólidos / Basuras</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>122+930</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>122+930</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Repintado de Postes de (hitos) kilométricos T2</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Repintado de Parapetos Muros T2</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>123+044</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>123+046</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de carril/pista y bermas T2</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>122+766</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>122+800</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Delineador T2</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>122+790</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>122+792</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Delineador T2</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>122+875</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>122+876</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Guardavías T2</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>122+900</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Año 2024 (3 registros)</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>123+030</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>123+100</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>123+044</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>123+046</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Postes de Señalización Vertical T2</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>122+920</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Año 2025 (8 registros)</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>122+750</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>122+800</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de carril/pista y bermas T2</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>122+900</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>122+870</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>123+020</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Reparación de Bache Superficial T2</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>122+900</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>122+935</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Repintado de Parapetos Muros T2</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>122+945</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cabezal de Alcantarilla T2</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>123+060</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>123+060</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>122+900</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Residuos Sólidos / Basuras</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>123+060</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>123+085</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Año 2026 (5 registros)</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>122+960</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>Remocion de Derrumbes T2</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>122+980</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>123+000</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Reparación de Bache Superficial T2</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>122+790</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>122+790</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>122+800</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>122+999</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Repintado de Parapetos Muros T2</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>122+945</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>122+940</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A72:F72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
